--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.90921889080827</v>
+        <v>4.697748069756345</v>
       </c>
       <c r="D2" t="n">
-        <v>30.18700382583663</v>
+        <v>4.905388121698453</v>
       </c>
       <c r="E2" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F2" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.87834855067624</v>
+        <v>2.41773163948489</v>
       </c>
       <c r="D3" t="n">
-        <v>14.61883085839098</v>
+        <v>2.375560014488535</v>
       </c>
       <c r="E3" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F3" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.44701146639575</v>
+        <v>5.760139363289309</v>
       </c>
       <c r="D4" t="n">
-        <v>14.70544116985274</v>
+        <v>2.38963419010107</v>
       </c>
       <c r="E4" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F4" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>16.85537458335572</v>
+        <v>2.738998369795305</v>
       </c>
       <c r="D5" t="n">
-        <v>16.70306374203803</v>
+        <v>2.714247858081181</v>
       </c>
       <c r="E5" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F5" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.97251292201249</v>
+        <v>4.220533349827029</v>
       </c>
       <c r="D6" t="n">
-        <v>25.90501550941416</v>
+        <v>4.209565020279801</v>
       </c>
       <c r="E6" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F6" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>48.8445644538061</v>
+        <v>7.937241723743492</v>
       </c>
       <c r="D7" t="n">
-        <v>20.43338204374472</v>
+        <v>3.320424582108517</v>
       </c>
       <c r="E7" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F7" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>37.76797944982179</v>
+        <v>6.137296660596042</v>
       </c>
       <c r="D8" t="n">
-        <v>23.87591651750834</v>
+        <v>3.879836434095106</v>
       </c>
       <c r="E8" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F8" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.37754666359676</v>
+        <v>6.073851332834474</v>
       </c>
       <c r="D9" t="n">
-        <v>15.58013862090996</v>
+        <v>2.531772525897868</v>
       </c>
       <c r="E9" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F9" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.39013200143204</v>
+        <v>5.588396450232706</v>
       </c>
       <c r="D10" t="n">
-        <v>12.48739333883193</v>
+        <v>2.029201417560189</v>
       </c>
       <c r="E10" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F10" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>47.38246022908797</v>
+        <v>7.699649787226795</v>
       </c>
       <c r="D11" t="n">
-        <v>9.067723544797968</v>
+        <v>1.47350507602967</v>
       </c>
       <c r="E11" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F11" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>74.53894019248702</v>
+        <v>12.11257778127914</v>
       </c>
       <c r="D12" t="n">
-        <v>73.70904285346377</v>
+        <v>11.97771946368786</v>
       </c>
       <c r="E12" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F12" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>36.05994676621528</v>
+        <v>5.859741349509982</v>
       </c>
       <c r="D13" t="n">
-        <v>22.43487635862482</v>
+        <v>3.645667408276534</v>
       </c>
       <c r="E13" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F13" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.80113226015874</v>
+        <v>4.355183992275795</v>
       </c>
       <c r="D14" t="n">
-        <v>26.50031148261667</v>
+        <v>4.306300615925209</v>
       </c>
       <c r="E14" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F14" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.05348243830112</v>
+        <v>9.271190896223931</v>
       </c>
       <c r="D15" t="n">
-        <v>56.55310107744166</v>
+        <v>9.189878925084271</v>
       </c>
       <c r="E15" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F15" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.36677937619022</v>
+        <v>2.822101648630911</v>
       </c>
       <c r="D16" t="n">
-        <v>19.12247217830581</v>
+        <v>3.107401728974694</v>
       </c>
       <c r="E16" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F16" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>32.72622151664341</v>
+        <v>5.318010996454554</v>
       </c>
       <c r="D17" t="n">
-        <v>31.85086753734549</v>
+        <v>5.175765974818642</v>
       </c>
       <c r="E17" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F17" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>23.142294759822</v>
+        <v>3.760622898471076</v>
       </c>
       <c r="D18" t="n">
-        <v>23.00920892976602</v>
+        <v>3.738996451086978</v>
       </c>
       <c r="E18" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F18" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30.17070047176677</v>
+        <v>4.9027388266621</v>
       </c>
       <c r="D19" t="n">
-        <v>28.41583115613939</v>
+        <v>4.617572562872651</v>
       </c>
       <c r="E19" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F19" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>40.85529020847436</v>
+        <v>6.638984658877083</v>
       </c>
       <c r="D20" t="n">
-        <v>40.30175703090649</v>
+        <v>6.549035517522304</v>
       </c>
       <c r="E20" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F20" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>39.13120318426694</v>
+        <v>6.358820517443378</v>
       </c>
       <c r="D21" t="n">
-        <v>37.43912828515172</v>
+        <v>6.083858346337155</v>
       </c>
       <c r="E21" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F21" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>49.11018178203343</v>
+        <v>7.980404539580433</v>
       </c>
       <c r="D22" t="n">
-        <v>47.55264353732453</v>
+        <v>7.727304574815236</v>
       </c>
       <c r="E22" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F22" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>67.80900485584944</v>
+        <v>11.01896328907553</v>
       </c>
       <c r="D23" t="n">
-        <v>67.57195116900196</v>
+        <v>10.98044206496282</v>
       </c>
       <c r="E23" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F23" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>74.49482033627633</v>
+        <v>12.10540830464491</v>
       </c>
       <c r="D24" t="n">
-        <v>74.06856962065115</v>
+        <v>12.03614256335581</v>
       </c>
       <c r="E24" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F24" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>40.41721302654278</v>
+        <v>6.567797116813202</v>
       </c>
       <c r="D25" t="n">
-        <v>39.26031146424209</v>
+        <v>6.379800612939341</v>
       </c>
       <c r="E25" t="n">
-        <v>16.23986215537059</v>
+        <v>2.638977600247721</v>
       </c>
       <c r="F25" t="n">
-        <v>18.7118496639899</v>
+        <v>3.040675570398358</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
